--- a/data-raw/NT/Forecasts.xlsx
+++ b/data-raw/NT/Forecasts.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\4983\Documents\tax4sa\data-raw\NT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7391EDD2-682C-44F1-A13D-159CA27822FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD8F5B2-7C3F-4C3A-AB0C-53214B66CB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tax revenue forecasts" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="50">
   <si>
     <t>Source</t>
   </si>
@@ -170,19 +181,24 @@
   <si>
     <t>2026/27</t>
   </si>
+  <si>
+    <t>2027/28</t>
+  </si>
+  <si>
+    <t>2028/29</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  <numFmts count="6">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="167" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="168" formatCode="_ [$€-2]\ * #,##0.00_ ;_ [$€-2]\ * \-#,##0.00_ ;_ [$€-2]\ * &quot;-&quot;??_ "/>
-    <numFmt numFmtId="172" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="42" x14ac:knownFonts="1">
     <font>
@@ -985,23 +1001,23 @@
   </borders>
   <cellStyleXfs count="375">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyFont="0"/>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyFont="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
@@ -1009,11 +1025,11 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
@@ -1022,7 +1038,7 @@
     <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1329,9 +1345,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
@@ -1345,7 +1361,7 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="41" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
@@ -1357,12 +1373,12 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1371,7 +1387,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="375">
     <cellStyle name="20% - Accent1 2" xfId="40" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2026,24 +2041,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB299"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AC328"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="14" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="13.90625" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="14" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.33203125" customWidth="1"/>
-    <col min="27" max="27" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.36328125" customWidth="1"/>
+    <col min="27" max="27" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.81640625" customWidth="1"/>
+    <col min="29" max="29" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2125,8 +2142,14 @@
       <c r="AA1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2168,7 +2191,7 @@
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2210,7 +2233,7 @@
       <c r="W3" s="2"/>
       <c r="X3" s="2"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2252,7 +2275,7 @@
       <c r="W4" s="2"/>
       <c r="X4" s="2"/>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2294,7 +2317,7 @@
       <c r="W5" s="2"/>
       <c r="X5" s="2"/>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2336,7 +2359,7 @@
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2378,7 +2401,7 @@
       <c r="W7" s="2"/>
       <c r="X7" s="2"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2420,7 +2443,7 @@
       <c r="W8" s="2"/>
       <c r="X8" s="2"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2462,7 +2485,7 @@
       <c r="W9" s="2"/>
       <c r="X9" s="2"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -2504,7 +2527,7 @@
       <c r="W10" s="2"/>
       <c r="X10" s="2"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -2546,7 +2569,7 @@
       <c r="W11" s="2"/>
       <c r="X11" s="2"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -2588,7 +2611,7 @@
       <c r="W12" s="2"/>
       <c r="X12" s="2"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -2630,7 +2653,7 @@
       <c r="W13" s="2"/>
       <c r="X13" s="2"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -2672,7 +2695,7 @@
       <c r="W14" s="2"/>
       <c r="X14" s="2"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -2714,7 +2737,7 @@
       <c r="W15" s="2"/>
       <c r="X15" s="2"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2756,7 +2779,7 @@
       <c r="W16" s="2"/>
       <c r="X16" s="2"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -2798,7 +2821,7 @@
       <c r="W17" s="2"/>
       <c r="X17" s="2"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -2840,7 +2863,7 @@
       <c r="W18" s="2"/>
       <c r="X18" s="2"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -2882,7 +2905,7 @@
       <c r="W19" s="2"/>
       <c r="X19" s="2"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -2924,7 +2947,7 @@
       <c r="W20" s="2"/>
       <c r="X20" s="2"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -2966,7 +2989,7 @@
       <c r="W21" s="2"/>
       <c r="X21" s="2"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -3008,7 +3031,7 @@
       <c r="W22" s="2"/>
       <c r="X22" s="2"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -3050,7 +3073,7 @@
       <c r="W23" s="2"/>
       <c r="X23" s="2"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -3092,7 +3115,7 @@
       <c r="W24" s="2"/>
       <c r="X24" s="2"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -3134,7 +3157,7 @@
       <c r="W25" s="2"/>
       <c r="X25" s="2"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -3176,7 +3199,7 @@
       <c r="W26" s="2"/>
       <c r="X26" s="2"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -3218,7 +3241,7 @@
       <c r="W27" s="2"/>
       <c r="X27" s="2"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -3260,7 +3283,7 @@
       <c r="W28" s="2"/>
       <c r="X28" s="2"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -3302,7 +3325,7 @@
       <c r="W29" s="2"/>
       <c r="X29" s="2"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -3344,7 +3367,7 @@
       <c r="W30" s="2"/>
       <c r="X30" s="2"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -3386,7 +3409,7 @@
       <c r="W31" s="2"/>
       <c r="X31" s="2"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -3428,7 +3451,7 @@
       <c r="W32" s="2"/>
       <c r="X32" s="2"/>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>3</v>
       </c>
@@ -3470,7 +3493,7 @@
       <c r="W33" s="2"/>
       <c r="X33" s="2"/>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>3</v>
       </c>
@@ -3512,7 +3535,7 @@
       <c r="W34" s="2"/>
       <c r="X34" s="2"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -3554,7 +3577,7 @@
       <c r="W35" s="2"/>
       <c r="X35" s="2"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>3</v>
       </c>
@@ -3596,7 +3619,7 @@
       <c r="W36" s="2"/>
       <c r="X36" s="2"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -3638,7 +3661,7 @@
       <c r="W37" s="2"/>
       <c r="X37" s="2"/>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -3680,7 +3703,7 @@
       <c r="W38" s="2"/>
       <c r="X38" s="2"/>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -3722,7 +3745,7 @@
       <c r="W39" s="2"/>
       <c r="X39" s="2"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -3764,7 +3787,7 @@
       <c r="W40" s="2"/>
       <c r="X40" s="2"/>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -3806,7 +3829,7 @@
       <c r="W41" s="2"/>
       <c r="X41" s="2"/>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -3848,7 +3871,7 @@
       <c r="W42" s="2"/>
       <c r="X42" s="2"/>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>3</v>
       </c>
@@ -3890,7 +3913,7 @@
       <c r="W43" s="2"/>
       <c r="X43" s="2"/>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>3</v>
       </c>
@@ -3932,7 +3955,7 @@
       <c r="W44" s="2"/>
       <c r="X44" s="2"/>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>3</v>
       </c>
@@ -3974,7 +3997,7 @@
       <c r="W45" s="2"/>
       <c r="X45" s="2"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>3</v>
       </c>
@@ -4016,7 +4039,7 @@
       <c r="W46" s="2"/>
       <c r="X46" s="2"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>3</v>
       </c>
@@ -4058,7 +4081,7 @@
       <c r="W47" s="2"/>
       <c r="X47" s="2"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>3</v>
       </c>
@@ -4100,7 +4123,7 @@
       <c r="W48" s="2"/>
       <c r="X48" s="2"/>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>3</v>
       </c>
@@ -4142,7 +4165,7 @@
       <c r="W49" s="2"/>
       <c r="X49" s="2"/>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>3</v>
       </c>
@@ -4184,7 +4207,7 @@
       <c r="W50" s="2"/>
       <c r="X50" s="2"/>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>3</v>
       </c>
@@ -4226,7 +4249,7 @@
       <c r="W51" s="2"/>
       <c r="X51" s="2"/>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>3</v>
       </c>
@@ -4268,7 +4291,7 @@
       <c r="W52" s="2"/>
       <c r="X52" s="2"/>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>3</v>
       </c>
@@ -4310,7 +4333,7 @@
       <c r="W53" s="2"/>
       <c r="X53" s="2"/>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>3</v>
       </c>
@@ -4352,7 +4375,7 @@
       <c r="W54" s="2"/>
       <c r="X54" s="2"/>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>3</v>
       </c>
@@ -4394,7 +4417,7 @@
       <c r="W55" s="2"/>
       <c r="X55" s="2"/>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>3</v>
       </c>
@@ -4436,7 +4459,7 @@
       <c r="W56" s="2"/>
       <c r="X56" s="2"/>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>3</v>
       </c>
@@ -4478,7 +4501,7 @@
       <c r="W57" s="2"/>
       <c r="X57" s="2"/>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>3</v>
       </c>
@@ -4516,7 +4539,7 @@
       <c r="W58" s="2"/>
       <c r="X58" s="2"/>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>3</v>
       </c>
@@ -4558,7 +4581,7 @@
       <c r="W59" s="2"/>
       <c r="X59" s="2"/>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>3</v>
       </c>
@@ -4600,7 +4623,7 @@
       <c r="W60" s="2"/>
       <c r="X60" s="2"/>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>3</v>
       </c>
@@ -4642,7 +4665,7 @@
       <c r="W61" s="2"/>
       <c r="X61" s="2"/>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>3</v>
       </c>
@@ -4684,7 +4707,7 @@
       <c r="W62" s="2"/>
       <c r="X62" s="2"/>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>3</v>
       </c>
@@ -4726,7 +4749,7 @@
       <c r="W63" s="2"/>
       <c r="X63" s="2"/>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>3</v>
       </c>
@@ -4768,7 +4791,7 @@
       <c r="W64" s="2"/>
       <c r="X64" s="2"/>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>3</v>
       </c>
@@ -4810,7 +4833,7 @@
       <c r="W65" s="2"/>
       <c r="X65" s="2"/>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>3</v>
       </c>
@@ -4852,7 +4875,7 @@
       <c r="W66" s="2"/>
       <c r="X66" s="2"/>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>3</v>
       </c>
@@ -4894,7 +4917,7 @@
       <c r="W67" s="2"/>
       <c r="X67" s="2"/>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>3</v>
       </c>
@@ -4936,7 +4959,7 @@
       <c r="W68" s="2"/>
       <c r="X68" s="2"/>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>3</v>
       </c>
@@ -4978,7 +5001,7 @@
       <c r="W69" s="2"/>
       <c r="X69" s="2"/>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>3</v>
       </c>
@@ -5020,7 +5043,7 @@
       <c r="W70" s="2"/>
       <c r="X70" s="2"/>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>3</v>
       </c>
@@ -5062,7 +5085,7 @@
       <c r="W71" s="2"/>
       <c r="X71" s="2"/>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>3</v>
       </c>
@@ -5104,7 +5127,7 @@
       <c r="W72" s="2"/>
       <c r="X72" s="2"/>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>3</v>
       </c>
@@ -5142,7 +5165,7 @@
       <c r="W73" s="2"/>
       <c r="X73" s="2"/>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>3</v>
       </c>
@@ -5184,7 +5207,7 @@
       <c r="W74" s="2"/>
       <c r="X74" s="2"/>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>3</v>
       </c>
@@ -5226,7 +5249,7 @@
       <c r="W75" s="2"/>
       <c r="X75" s="2"/>
     </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>3</v>
       </c>
@@ -5268,7 +5291,7 @@
       <c r="W76" s="2"/>
       <c r="X76" s="2"/>
     </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>3</v>
       </c>
@@ -5310,7 +5333,7 @@
       <c r="W77" s="2"/>
       <c r="X77" s="2"/>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>3</v>
       </c>
@@ -5352,7 +5375,7 @@
       <c r="W78" s="2"/>
       <c r="X78" s="2"/>
     </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>3</v>
       </c>
@@ -5394,7 +5417,7 @@
       <c r="W79" s="2"/>
       <c r="X79" s="2"/>
     </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>3</v>
       </c>
@@ -5436,7 +5459,7 @@
       <c r="W80" s="2"/>
       <c r="X80" s="2"/>
     </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>3</v>
       </c>
@@ -5478,7 +5501,7 @@
       <c r="W81" s="2"/>
       <c r="X81" s="2"/>
     </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>3</v>
       </c>
@@ -5520,7 +5543,7 @@
       <c r="W82" s="2"/>
       <c r="X82" s="2"/>
     </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>3</v>
       </c>
@@ -5562,7 +5585,7 @@
       <c r="W83" s="2"/>
       <c r="X83" s="2"/>
     </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>3</v>
       </c>
@@ -5604,7 +5627,7 @@
       <c r="W84" s="2"/>
       <c r="X84" s="2"/>
     </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>3</v>
       </c>
@@ -5646,7 +5669,7 @@
       <c r="W85" s="2"/>
       <c r="X85" s="2"/>
     </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>3</v>
       </c>
@@ -5688,7 +5711,7 @@
       <c r="W86" s="2"/>
       <c r="X86" s="2"/>
     </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>3</v>
       </c>
@@ -5730,7 +5753,7 @@
       <c r="W87" s="2"/>
       <c r="X87" s="2"/>
     </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>3</v>
       </c>
@@ -5768,7 +5791,7 @@
       <c r="W88" s="2"/>
       <c r="X88" s="2"/>
     </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>3</v>
       </c>
@@ -5810,7 +5833,7 @@
       <c r="W89" s="2"/>
       <c r="X89" s="2"/>
     </row>
-    <row r="90" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>3</v>
       </c>
@@ -5852,7 +5875,7 @@
       <c r="W90" s="2"/>
       <c r="X90" s="2"/>
     </row>
-    <row r="91" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>3</v>
       </c>
@@ -5894,7 +5917,7 @@
       <c r="W91" s="2"/>
       <c r="X91" s="2"/>
     </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>3</v>
       </c>
@@ -5936,7 +5959,7 @@
       <c r="W92" s="2"/>
       <c r="X92" s="2"/>
     </row>
-    <row r="93" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>3</v>
       </c>
@@ -5978,7 +6001,7 @@
       <c r="W93" s="2"/>
       <c r="X93" s="2"/>
     </row>
-    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>3</v>
       </c>
@@ -6020,7 +6043,7 @@
       <c r="W94" s="2"/>
       <c r="X94" s="2"/>
     </row>
-    <row r="95" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>3</v>
       </c>
@@ -6062,7 +6085,7 @@
       <c r="W95" s="2"/>
       <c r="X95" s="2"/>
     </row>
-    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>3</v>
       </c>
@@ -6104,7 +6127,7 @@
       <c r="W96" s="2"/>
       <c r="X96" s="2"/>
     </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>3</v>
       </c>
@@ -6146,7 +6169,7 @@
       <c r="W97" s="2"/>
       <c r="X97" s="2"/>
     </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>3</v>
       </c>
@@ -6188,7 +6211,7 @@
       <c r="W98" s="2"/>
       <c r="X98" s="2"/>
     </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>3</v>
       </c>
@@ -6230,7 +6253,7 @@
       <c r="W99" s="2"/>
       <c r="X99" s="2"/>
     </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>3</v>
       </c>
@@ -6272,7 +6295,7 @@
       <c r="W100" s="2"/>
       <c r="X100" s="2"/>
     </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>3</v>
       </c>
@@ -6314,7 +6337,7 @@
       <c r="W101" s="2"/>
       <c r="X101" s="2"/>
     </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>3</v>
       </c>
@@ -6356,7 +6379,7 @@
       <c r="W102" s="2"/>
       <c r="X102" s="2"/>
     </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>3</v>
       </c>
@@ -6394,7 +6417,7 @@
       <c r="W103" s="2"/>
       <c r="X103" s="2"/>
     </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>3</v>
       </c>
@@ -6436,7 +6459,7 @@
       <c r="W104" s="2"/>
       <c r="X104" s="2"/>
     </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>3</v>
       </c>
@@ -6478,7 +6501,7 @@
       <c r="W105" s="2"/>
       <c r="X105" s="2"/>
     </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>3</v>
       </c>
@@ -6520,7 +6543,7 @@
       <c r="W106" s="2"/>
       <c r="X106" s="2"/>
     </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>3</v>
       </c>
@@ -6562,7 +6585,7 @@
       <c r="W107" s="2"/>
       <c r="X107" s="2"/>
     </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>3</v>
       </c>
@@ -6604,7 +6627,7 @@
       <c r="W108" s="2"/>
       <c r="X108" s="2"/>
     </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>3</v>
       </c>
@@ -6646,7 +6669,7 @@
       <c r="W109" s="2"/>
       <c r="X109" s="2"/>
     </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>3</v>
       </c>
@@ -6688,7 +6711,7 @@
       <c r="W110" s="2"/>
       <c r="X110" s="2"/>
     </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>3</v>
       </c>
@@ -6730,7 +6753,7 @@
       <c r="W111" s="2"/>
       <c r="X111" s="2"/>
     </row>
-    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>3</v>
       </c>
@@ -6772,7 +6795,7 @@
       <c r="W112" s="2"/>
       <c r="X112" s="2"/>
     </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>3</v>
       </c>
@@ -6814,7 +6837,7 @@
       <c r="W113" s="2"/>
       <c r="X113" s="2"/>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>3</v>
       </c>
@@ -6856,7 +6879,7 @@
       <c r="W114" s="2"/>
       <c r="X114" s="2"/>
     </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>3</v>
       </c>
@@ -6898,7 +6921,7 @@
       <c r="W115" s="2"/>
       <c r="X115" s="2"/>
     </row>
-    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>3</v>
       </c>
@@ -6940,7 +6963,7 @@
       <c r="W116" s="2"/>
       <c r="X116" s="2"/>
     </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>3</v>
       </c>
@@ -6982,7 +7005,7 @@
       <c r="W117" s="2"/>
       <c r="X117" s="2"/>
     </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>3</v>
       </c>
@@ -7020,7 +7043,7 @@
       <c r="W118" s="2"/>
       <c r="X118" s="2"/>
     </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>3</v>
       </c>
@@ -7062,7 +7085,7 @@
       <c r="W119" s="2"/>
       <c r="X119" s="2"/>
     </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>3</v>
       </c>
@@ -7104,7 +7127,7 @@
       <c r="W120" s="2"/>
       <c r="X120" s="2"/>
     </row>
-    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>3</v>
       </c>
@@ -7146,7 +7169,7 @@
       <c r="W121" s="2"/>
       <c r="X121" s="2"/>
     </row>
-    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>3</v>
       </c>
@@ -7188,7 +7211,7 @@
       <c r="W122" s="2"/>
       <c r="X122" s="2"/>
     </row>
-    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>3</v>
       </c>
@@ -7230,7 +7253,7 @@
       <c r="W123" s="2"/>
       <c r="X123" s="2"/>
     </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>3</v>
       </c>
@@ -7272,7 +7295,7 @@
       <c r="W124" s="2"/>
       <c r="X124" s="2"/>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>3</v>
       </c>
@@ -7314,7 +7337,7 @@
       <c r="W125" s="2"/>
       <c r="X125" s="2"/>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>3</v>
       </c>
@@ -7356,7 +7379,7 @@
       <c r="W126" s="2"/>
       <c r="X126" s="2"/>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>3</v>
       </c>
@@ -7398,7 +7421,7 @@
       <c r="W127" s="2"/>
       <c r="X127" s="2"/>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>3</v>
       </c>
@@ -7440,7 +7463,7 @@
       <c r="W128" s="2"/>
       <c r="X128" s="2"/>
     </row>
-    <row r="129" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>3</v>
       </c>
@@ -7482,7 +7505,7 @@
       <c r="W129" s="2"/>
       <c r="X129" s="2"/>
     </row>
-    <row r="130" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>3</v>
       </c>
@@ -7524,7 +7547,7 @@
       <c r="W130" s="2"/>
       <c r="X130" s="2"/>
     </row>
-    <row r="131" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>3</v>
       </c>
@@ -7566,7 +7589,7 @@
       <c r="W131" s="2"/>
       <c r="X131" s="2"/>
     </row>
-    <row r="132" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>3</v>
       </c>
@@ -7608,7 +7631,7 @@
       <c r="W132" s="2"/>
       <c r="X132" s="2"/>
     </row>
-    <row r="133" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>3</v>
       </c>
@@ -7646,7 +7669,7 @@
       <c r="W133" s="2"/>
       <c r="X133" s="2"/>
     </row>
-    <row r="134" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>3</v>
       </c>
@@ -7688,7 +7711,7 @@
       <c r="W134" s="2"/>
       <c r="X134" s="2"/>
     </row>
-    <row r="135" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>3</v>
       </c>
@@ -7730,7 +7753,7 @@
       <c r="W135" s="2"/>
       <c r="X135" s="2"/>
     </row>
-    <row r="136" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>3</v>
       </c>
@@ -7772,7 +7795,7 @@
       <c r="W136" s="2"/>
       <c r="X136" s="2"/>
     </row>
-    <row r="137" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>3</v>
       </c>
@@ -7814,7 +7837,7 @@
       <c r="W137" s="2"/>
       <c r="X137" s="2"/>
     </row>
-    <row r="138" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>3</v>
       </c>
@@ -7856,7 +7879,7 @@
       <c r="W138" s="2"/>
       <c r="X138" s="2"/>
     </row>
-    <row r="139" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>3</v>
       </c>
@@ -7898,7 +7921,7 @@
       <c r="W139" s="2"/>
       <c r="X139" s="2"/>
     </row>
-    <row r="140" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>3</v>
       </c>
@@ -7940,7 +7963,7 @@
       <c r="W140" s="2"/>
       <c r="X140" s="2"/>
     </row>
-    <row r="141" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>3</v>
       </c>
@@ -7982,7 +8005,7 @@
       <c r="W141" s="2"/>
       <c r="X141" s="2"/>
     </row>
-    <row r="142" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>3</v>
       </c>
@@ -8024,7 +8047,7 @@
       <c r="W142" s="2"/>
       <c r="X142" s="2"/>
     </row>
-    <row r="143" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>3</v>
       </c>
@@ -8066,7 +8089,7 @@
       <c r="W143" s="2"/>
       <c r="X143" s="2"/>
     </row>
-    <row r="144" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>3</v>
       </c>
@@ -8108,7 +8131,7 @@
       <c r="W144" s="2"/>
       <c r="X144" s="2"/>
     </row>
-    <row r="145" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>3</v>
       </c>
@@ -8150,7 +8173,7 @@
       <c r="W145" s="2"/>
       <c r="X145" s="2"/>
     </row>
-    <row r="146" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>3</v>
       </c>
@@ -8192,7 +8215,7 @@
       <c r="W146" s="2"/>
       <c r="X146" s="2"/>
     </row>
-    <row r="147" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>3</v>
       </c>
@@ -8234,7 +8257,7 @@
       <c r="W147" s="2"/>
       <c r="X147" s="2"/>
     </row>
-    <row r="148" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>3</v>
       </c>
@@ -8272,7 +8295,7 @@
       <c r="W148" s="2"/>
       <c r="X148" s="2"/>
     </row>
-    <row r="149" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>3</v>
       </c>
@@ -8314,7 +8337,7 @@
       <c r="W149" s="2"/>
       <c r="X149" s="2"/>
     </row>
-    <row r="150" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>3</v>
       </c>
@@ -8356,7 +8379,7 @@
       <c r="W150" s="2"/>
       <c r="X150" s="2"/>
     </row>
-    <row r="151" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>3</v>
       </c>
@@ -8398,7 +8421,7 @@
       <c r="W151" s="2"/>
       <c r="X151" s="2"/>
     </row>
-    <row r="152" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>3</v>
       </c>
@@ -8440,7 +8463,7 @@
       <c r="W152" s="2"/>
       <c r="X152" s="2"/>
     </row>
-    <row r="153" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>3</v>
       </c>
@@ -8482,7 +8505,7 @@
       <c r="W153" s="2"/>
       <c r="X153" s="2"/>
     </row>
-    <row r="154" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>3</v>
       </c>
@@ -8524,7 +8547,7 @@
       <c r="W154" s="2"/>
       <c r="X154" s="2"/>
     </row>
-    <row r="155" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>3</v>
       </c>
@@ -8566,7 +8589,7 @@
       <c r="W155" s="2"/>
       <c r="X155" s="2"/>
     </row>
-    <row r="156" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>3</v>
       </c>
@@ -8608,7 +8631,7 @@
       <c r="W156" s="2"/>
       <c r="X156" s="2"/>
     </row>
-    <row r="157" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>3</v>
       </c>
@@ -8650,7 +8673,7 @@
       <c r="W157" s="2"/>
       <c r="X157" s="2"/>
     </row>
-    <row r="158" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>3</v>
       </c>
@@ -8692,7 +8715,7 @@
       <c r="W158" s="2"/>
       <c r="X158" s="2"/>
     </row>
-    <row r="159" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>3</v>
       </c>
@@ -8734,7 +8757,7 @@
       <c r="W159" s="2"/>
       <c r="X159" s="2"/>
     </row>
-    <row r="160" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>3</v>
       </c>
@@ -8776,7 +8799,7 @@
       <c r="W160" s="2"/>
       <c r="X160" s="2"/>
     </row>
-    <row r="161" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>3</v>
       </c>
@@ -8818,7 +8841,7 @@
       <c r="W161" s="2"/>
       <c r="X161" s="2"/>
     </row>
-    <row r="162" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>3</v>
       </c>
@@ -8860,7 +8883,7 @@
       <c r="W162" s="2"/>
       <c r="X162" s="2"/>
     </row>
-    <row r="163" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>3</v>
       </c>
@@ -8898,7 +8921,7 @@
       <c r="W163" s="2"/>
       <c r="X163" s="2"/>
     </row>
-    <row r="164" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>3</v>
       </c>
@@ -8940,7 +8963,7 @@
       <c r="W164" s="2"/>
       <c r="X164" s="2"/>
     </row>
-    <row r="165" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>3</v>
       </c>
@@ -8982,7 +9005,7 @@
       <c r="W165" s="2"/>
       <c r="X165" s="2"/>
     </row>
-    <row r="166" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>3</v>
       </c>
@@ -9024,7 +9047,7 @@
       <c r="W166" s="2"/>
       <c r="X166" s="2"/>
     </row>
-    <row r="167" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>3</v>
       </c>
@@ -9066,7 +9089,7 @@
       <c r="W167" s="2"/>
       <c r="X167" s="2"/>
     </row>
-    <row r="168" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>3</v>
       </c>
@@ -9108,7 +9131,7 @@
       <c r="W168" s="2"/>
       <c r="X168" s="2"/>
     </row>
-    <row r="169" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>3</v>
       </c>
@@ -9150,7 +9173,7 @@
       <c r="W169" s="2"/>
       <c r="X169" s="2"/>
     </row>
-    <row r="170" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>3</v>
       </c>
@@ -9192,7 +9215,7 @@
       <c r="W170" s="2"/>
       <c r="X170" s="2"/>
     </row>
-    <row r="171" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>3</v>
       </c>
@@ -9234,7 +9257,7 @@
       <c r="W171" s="2"/>
       <c r="X171" s="2"/>
     </row>
-    <row r="172" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>3</v>
       </c>
@@ -9276,7 +9299,7 @@
       <c r="W172" s="2"/>
       <c r="X172" s="2"/>
     </row>
-    <row r="173" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>3</v>
       </c>
@@ -9318,7 +9341,7 @@
       <c r="W173" s="2"/>
       <c r="X173" s="2"/>
     </row>
-    <row r="174" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>3</v>
       </c>
@@ -9360,7 +9383,7 @@
       <c r="W174" s="2"/>
       <c r="X174" s="2"/>
     </row>
-    <row r="175" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>3</v>
       </c>
@@ -9402,7 +9425,7 @@
       <c r="W175" s="2"/>
       <c r="X175" s="2"/>
     </row>
-    <row r="176" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>3</v>
       </c>
@@ -9444,7 +9467,7 @@
       <c r="W176" s="2"/>
       <c r="X176" s="2"/>
     </row>
-    <row r="177" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>3</v>
       </c>
@@ -9486,7 +9509,7 @@
       <c r="W177" s="2"/>
       <c r="X177" s="2"/>
     </row>
-    <row r="178" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>3</v>
       </c>
@@ -9524,7 +9547,7 @@
       <c r="W178" s="2"/>
       <c r="X178" s="2"/>
     </row>
-    <row r="179" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>3</v>
       </c>
@@ -9568,7 +9591,7 @@
       <c r="W179" s="2"/>
       <c r="X179" s="2"/>
     </row>
-    <row r="180" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>3</v>
       </c>
@@ -9610,7 +9633,7 @@
       <c r="W180" s="2"/>
       <c r="X180" s="2"/>
     </row>
-    <row r="181" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>3</v>
       </c>
@@ -9652,7 +9675,7 @@
       <c r="W181" s="2"/>
       <c r="X181" s="2"/>
     </row>
-    <row r="182" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>3</v>
       </c>
@@ -9694,7 +9717,7 @@
       <c r="W182" s="2"/>
       <c r="X182" s="2"/>
     </row>
-    <row r="183" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>3</v>
       </c>
@@ -9736,7 +9759,7 @@
       <c r="W183" s="2"/>
       <c r="X183" s="2"/>
     </row>
-    <row r="184" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>3</v>
       </c>
@@ -9778,7 +9801,7 @@
       <c r="W184" s="2"/>
       <c r="X184" s="2"/>
     </row>
-    <row r="185" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>3</v>
       </c>
@@ -9820,7 +9843,7 @@
       <c r="W185" s="2"/>
       <c r="X185" s="2"/>
     </row>
-    <row r="186" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>3</v>
       </c>
@@ -9862,7 +9885,7 @@
       <c r="W186" s="2"/>
       <c r="X186" s="2"/>
     </row>
-    <row r="187" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>3</v>
       </c>
@@ -9904,7 +9927,7 @@
       <c r="W187" s="2"/>
       <c r="X187" s="2"/>
     </row>
-    <row r="188" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>3</v>
       </c>
@@ -9946,7 +9969,7 @@
       <c r="W188" s="2"/>
       <c r="X188" s="2"/>
     </row>
-    <row r="189" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>3</v>
       </c>
@@ -9988,7 +10011,7 @@
       <c r="W189" s="2"/>
       <c r="X189" s="2"/>
     </row>
-    <row r="190" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>3</v>
       </c>
@@ -10030,7 +10053,7 @@
       <c r="W190" s="2"/>
       <c r="X190" s="2"/>
     </row>
-    <row r="191" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>3</v>
       </c>
@@ -10072,7 +10095,7 @@
       <c r="W191" s="2"/>
       <c r="X191" s="2"/>
     </row>
-    <row r="192" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>3</v>
       </c>
@@ -10114,7 +10137,7 @@
       <c r="W192" s="2"/>
       <c r="X192" s="2"/>
     </row>
-    <row r="193" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>3</v>
       </c>
@@ -10152,7 +10175,7 @@
       <c r="W193" s="2"/>
       <c r="X193" s="2"/>
     </row>
-    <row r="194" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>3</v>
       </c>
@@ -10194,7 +10217,7 @@
       <c r="W194" s="2"/>
       <c r="X194" s="2"/>
     </row>
-    <row r="195" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>3</v>
       </c>
@@ -10236,7 +10259,7 @@
       <c r="W195" s="2"/>
       <c r="X195" s="2"/>
     </row>
-    <row r="196" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>3</v>
       </c>
@@ -10278,7 +10301,7 @@
       <c r="W196" s="2"/>
       <c r="X196" s="2"/>
     </row>
-    <row r="197" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>3</v>
       </c>
@@ -10320,7 +10343,7 @@
       <c r="W197" s="2"/>
       <c r="X197" s="2"/>
     </row>
-    <row r="198" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>3</v>
       </c>
@@ -10362,7 +10385,7 @@
       <c r="W198" s="2"/>
       <c r="X198" s="2"/>
     </row>
-    <row r="199" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>3</v>
       </c>
@@ -10404,7 +10427,7 @@
       <c r="W199" s="2"/>
       <c r="X199" s="2"/>
     </row>
-    <row r="200" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>3</v>
       </c>
@@ -10446,7 +10469,7 @@
       <c r="W200" s="2"/>
       <c r="X200" s="2"/>
     </row>
-    <row r="201" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>3</v>
       </c>
@@ -10488,7 +10511,7 @@
       <c r="W201" s="2"/>
       <c r="X201" s="2"/>
     </row>
-    <row r="202" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>3</v>
       </c>
@@ -10530,7 +10553,7 @@
       <c r="W202" s="2"/>
       <c r="X202" s="2"/>
     </row>
-    <row r="203" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>3</v>
       </c>
@@ -10572,7 +10595,7 @@
       <c r="W203" s="2"/>
       <c r="X203" s="2"/>
     </row>
-    <row r="204" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>3</v>
       </c>
@@ -10614,7 +10637,7 @@
       <c r="W204" s="2"/>
       <c r="X204" s="2"/>
     </row>
-    <row r="205" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>3</v>
       </c>
@@ -10656,7 +10679,7 @@
       <c r="W205" s="2"/>
       <c r="X205" s="2"/>
     </row>
-    <row r="206" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>3</v>
       </c>
@@ -10698,7 +10721,7 @@
       <c r="W206" s="2"/>
       <c r="X206" s="2"/>
     </row>
-    <row r="207" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>3</v>
       </c>
@@ -10740,7 +10763,7 @@
       <c r="W207" s="2"/>
       <c r="X207" s="2"/>
     </row>
-    <row r="208" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>3</v>
       </c>
@@ -10778,7 +10801,7 @@
       <c r="W208" s="2"/>
       <c r="X208" s="2"/>
     </row>
-    <row r="209" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>3</v>
       </c>
@@ -10820,7 +10843,7 @@
       <c r="W209" s="2"/>
       <c r="X209" s="2"/>
     </row>
-    <row r="210" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>3</v>
       </c>
@@ -10862,7 +10885,7 @@
       <c r="W210" s="2"/>
       <c r="X210" s="2"/>
     </row>
-    <row r="211" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>3</v>
       </c>
@@ -10904,7 +10927,7 @@
       <c r="W211" s="2"/>
       <c r="X211" s="2"/>
     </row>
-    <row r="212" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>3</v>
       </c>
@@ -10946,7 +10969,7 @@
       <c r="W212" s="2"/>
       <c r="X212" s="2"/>
     </row>
-    <row r="213" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>3</v>
       </c>
@@ -10988,7 +11011,7 @@
       <c r="W213" s="2"/>
       <c r="X213" s="2"/>
     </row>
-    <row r="214" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>3</v>
       </c>
@@ -11030,7 +11053,7 @@
       <c r="W214" s="2"/>
       <c r="X214" s="2"/>
     </row>
-    <row r="215" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>3</v>
       </c>
@@ -11072,7 +11095,7 @@
       <c r="W215" s="2"/>
       <c r="X215" s="2"/>
     </row>
-    <row r="216" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>3</v>
       </c>
@@ -11114,7 +11137,7 @@
       <c r="W216" s="2"/>
       <c r="X216" s="2"/>
     </row>
-    <row r="217" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>3</v>
       </c>
@@ -11156,7 +11179,7 @@
       <c r="W217" s="2"/>
       <c r="X217" s="2"/>
     </row>
-    <row r="218" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>3</v>
       </c>
@@ -11198,7 +11221,7 @@
       <c r="W218" s="2"/>
       <c r="X218" s="2"/>
     </row>
-    <row r="219" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>3</v>
       </c>
@@ -11240,7 +11263,7 @@
       <c r="W219" s="2"/>
       <c r="X219" s="2"/>
     </row>
-    <row r="220" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>3</v>
       </c>
@@ -11282,7 +11305,7 @@
       <c r="W220" s="2"/>
       <c r="X220" s="2"/>
     </row>
-    <row r="221" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>3</v>
       </c>
@@ -11324,7 +11347,7 @@
       <c r="W221" s="2"/>
       <c r="X221" s="2"/>
     </row>
-    <row r="222" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>3</v>
       </c>
@@ -11366,7 +11389,7 @@
       <c r="W222" s="2"/>
       <c r="X222" s="2"/>
     </row>
-    <row r="223" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>3</v>
       </c>
@@ -11394,7 +11417,7 @@
       <c r="W223" s="2"/>
       <c r="X223" s="2"/>
     </row>
-    <row r="224" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>3</v>
       </c>
@@ -11436,7 +11459,7 @@
       </c>
       <c r="X224" s="2"/>
     </row>
-    <row r="225" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>3</v>
       </c>
@@ -11478,7 +11501,7 @@
       </c>
       <c r="X225" s="2"/>
     </row>
-    <row r="226" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>3</v>
       </c>
@@ -11520,7 +11543,7 @@
       </c>
       <c r="X226" s="2"/>
     </row>
-    <row r="227" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>3</v>
       </c>
@@ -11562,7 +11585,7 @@
       </c>
       <c r="X227" s="2"/>
     </row>
-    <row r="228" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>3</v>
       </c>
@@ -11604,7 +11627,7 @@
       </c>
       <c r="X228" s="2"/>
     </row>
-    <row r="229" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>3</v>
       </c>
@@ -11646,7 +11669,7 @@
       </c>
       <c r="X229" s="2"/>
     </row>
-    <row r="230" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>3</v>
       </c>
@@ -11688,7 +11711,7 @@
       </c>
       <c r="X230" s="2"/>
     </row>
-    <row r="231" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>3</v>
       </c>
@@ -11730,7 +11753,7 @@
       </c>
       <c r="X231" s="2"/>
     </row>
-    <row r="232" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>3</v>
       </c>
@@ -11772,7 +11795,7 @@
       </c>
       <c r="X232" s="2"/>
     </row>
-    <row r="233" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>3</v>
       </c>
@@ -11814,7 +11837,7 @@
       </c>
       <c r="X233" s="2"/>
     </row>
-    <row r="234" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>3</v>
       </c>
@@ -11856,7 +11879,7 @@
       </c>
       <c r="X234" s="2"/>
     </row>
-    <row r="235" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>3</v>
       </c>
@@ -11898,7 +11921,7 @@
       </c>
       <c r="X235" s="2"/>
     </row>
-    <row r="236" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>3</v>
       </c>
@@ -11940,7 +11963,7 @@
       </c>
       <c r="X236" s="2"/>
     </row>
-    <row r="237" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>3</v>
       </c>
@@ -11982,7 +12005,7 @@
       </c>
       <c r="X237" s="2"/>
     </row>
-    <row r="238" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>3</v>
       </c>
@@ -12008,7 +12031,7 @@
         <v>1.0109999999999999</v>
       </c>
     </row>
-    <row r="239" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>3</v>
       </c>
@@ -12050,7 +12073,7 @@
         <v>861046.79</v>
       </c>
     </row>
-    <row r="240" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>3</v>
       </c>
@@ -12092,7 +12115,7 @@
         <v>587799.94200000004</v>
       </c>
     </row>
-    <row r="241" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>3</v>
       </c>
@@ -12134,7 +12157,7 @@
         <v>236826.03099999999</v>
       </c>
     </row>
-    <row r="242" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>3</v>
       </c>
@@ -12176,7 +12199,7 @@
         <v>20762.707999999999</v>
       </c>
     </row>
-    <row r="243" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>3</v>
       </c>
@@ -12218,7 +12241,7 @@
         <v>18713.760999999999</v>
       </c>
     </row>
-    <row r="244" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>3</v>
       </c>
@@ -12260,7 +12283,7 @@
         <v>587078.84400000004</v>
       </c>
     </row>
-    <row r="245" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>3</v>
       </c>
@@ -12301,7 +12324,7 @@
         <v>425422.23100000003</v>
       </c>
     </row>
-    <row r="246" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>3</v>
       </c>
@@ -12342,7 +12365,7 @@
         <v>60910.271999999997</v>
       </c>
     </row>
-    <row r="247" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>3</v>
       </c>
@@ -12383,7 +12406,7 @@
         <v>1548512.378</v>
       </c>
     </row>
-    <row r="248" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>3</v>
       </c>
@@ -12424,7 +12447,7 @@
         <v>31496.521000000001</v>
       </c>
     </row>
-    <row r="249" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>3</v>
       </c>
@@ -12465,7 +12488,7 @@
         <v>-57973.968999999997</v>
       </c>
     </row>
-    <row r="250" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>3</v>
       </c>
@@ -12506,7 +12529,7 @@
         <v>1522034.93</v>
       </c>
     </row>
-    <row r="251" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>3</v>
       </c>
@@ -12547,7 +12570,7 @@
         <v>0.254</v>
       </c>
     </row>
-    <row r="252" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>3</v>
       </c>
@@ -12588,7 +12611,7 @@
         <v>5997.1549999999997</v>
       </c>
     </row>
-    <row r="253" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>3</v>
       </c>
@@ -12614,7 +12637,7 @@
         <v>1.0680000000000001</v>
       </c>
     </row>
-    <row r="254" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>3</v>
       </c>
@@ -12640,7 +12663,7 @@
         <v>1003971.683</v>
       </c>
     </row>
-    <row r="255" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>3</v>
       </c>
@@ -12666,7 +12689,7 @@
         <v>678296.11300000001</v>
       </c>
     </row>
-    <row r="256" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>3</v>
       </c>
@@ -12692,7 +12715,7 @@
         <v>286096.86099999998</v>
       </c>
     </row>
-    <row r="257" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>3</v>
       </c>
@@ -12718,7 +12741,7 @@
         <v>24099.151000000002</v>
       </c>
     </row>
-    <row r="258" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>3</v>
       </c>
@@ -12744,7 +12767,7 @@
         <v>22787.474999999999</v>
       </c>
     </row>
-    <row r="259" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>3</v>
       </c>
@@ -12770,7 +12793,7 @@
         <v>685483.11100000003</v>
       </c>
     </row>
-    <row r="260" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>3</v>
       </c>
@@ -12796,7 +12819,7 @@
         <v>505006.64799999999</v>
       </c>
     </row>
-    <row r="261" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>3</v>
       </c>
@@ -12822,7 +12845,7 @@
         <v>71272.414999999994</v>
       </c>
     </row>
-    <row r="262" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>3</v>
       </c>
@@ -12848,7 +12871,7 @@
         <v>1807613.835</v>
       </c>
     </row>
-    <row r="263" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>3</v>
       </c>
@@ -12874,7 +12897,7 @@
         <v>32013.195</v>
       </c>
     </row>
-    <row r="264" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>3</v>
       </c>
@@ -12900,7 +12923,7 @@
         <v>-65452.608</v>
       </c>
     </row>
-    <row r="265" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>3</v>
       </c>
@@ -12926,7 +12949,7 @@
         <v>1774174.423</v>
       </c>
     </row>
-    <row r="266" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>3</v>
       </c>
@@ -12952,7 +12975,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="267" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>3</v>
       </c>
@@ -12978,7 +13001,7 @@
         <v>7233.7160000000003</v>
       </c>
     </row>
-    <row r="268" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>3</v>
       </c>
@@ -13004,7 +13027,7 @@
         <v>1.0629999999999999</v>
       </c>
     </row>
-    <row r="269" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>3</v>
       </c>
@@ -13030,7 +13053,7 @@
         <v>1172033</v>
       </c>
     </row>
-    <row r="270" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>3</v>
       </c>
@@ -13056,7 +13079,7 @@
         <v>752627</v>
       </c>
     </row>
-    <row r="271" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>3</v>
       </c>
@@ -13082,7 +13105,7 @@
         <v>369477</v>
       </c>
     </row>
-    <row r="272" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>3</v>
       </c>
@@ -13108,7 +13131,7 @@
         <v>26846</v>
       </c>
     </row>
-    <row r="273" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>3</v>
       </c>
@@ -13134,7 +13157,7 @@
         <v>27040</v>
       </c>
     </row>
-    <row r="274" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>3</v>
       </c>
@@ -13160,7 +13183,7 @@
         <v>731032</v>
       </c>
     </row>
-    <row r="275" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>3</v>
       </c>
@@ -13186,7 +13209,7 @@
         <v>537868</v>
       </c>
     </row>
-    <row r="276" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>3</v>
       </c>
@@ -13212,7 +13235,7 @@
         <v>86506</v>
       </c>
     </row>
-    <row r="277" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>3</v>
       </c>
@@ -13238,7 +13261,7 @@
         <v>2043456</v>
       </c>
     </row>
-    <row r="278" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>3</v>
       </c>
@@ -13264,7 +13287,7 @@
         <v>44310</v>
       </c>
     </row>
-    <row r="279" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>3</v>
       </c>
@@ -13290,7 +13313,7 @@
         <v>-80059</v>
       </c>
     </row>
-    <row r="280" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>3</v>
       </c>
@@ -13316,7 +13339,7 @@
         <v>2007707</v>
       </c>
     </row>
-    <row r="281" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>3</v>
       </c>
@@ -13342,7 +13365,7 @@
         <v>0.25700000000000001</v>
       </c>
     </row>
-    <row r="282" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>3</v>
       </c>
@@ -13368,7 +13391,7 @@
         <v>7938.5</v>
       </c>
     </row>
-    <row r="283" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>3</v>
       </c>
@@ -13394,7 +13417,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>3</v>
       </c>
@@ -13421,7 +13444,7 @@
       </c>
       <c r="AB284" s="4"/>
     </row>
-    <row r="285" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>3</v>
       </c>
@@ -13448,7 +13471,7 @@
       </c>
       <c r="AB285" s="4"/>
     </row>
-    <row r="286" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>3</v>
       </c>
@@ -13475,7 +13498,7 @@
       </c>
       <c r="AB286" s="4"/>
     </row>
-    <row r="287" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>3</v>
       </c>
@@ -13502,7 +13525,7 @@
       </c>
       <c r="AB287" s="4"/>
     </row>
-    <row r="288" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>3</v>
       </c>
@@ -13529,7 +13552,7 @@
       </c>
       <c r="AB288" s="4"/>
     </row>
-    <row r="289" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>3</v>
       </c>
@@ -13556,7 +13579,7 @@
       </c>
       <c r="AB289" s="4"/>
     </row>
-    <row r="290" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>3</v>
       </c>
@@ -13583,7 +13606,7 @@
       </c>
       <c r="AB290" s="4"/>
     </row>
-    <row r="291" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>3</v>
       </c>
@@ -13610,7 +13633,7 @@
       </c>
       <c r="AB291" s="4"/>
     </row>
-    <row r="292" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>3</v>
       </c>
@@ -13637,7 +13660,7 @@
       </c>
       <c r="AB292" s="4"/>
     </row>
-    <row r="293" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>3</v>
       </c>
@@ -13664,7 +13687,7 @@
       </c>
       <c r="AB293" s="4"/>
     </row>
-    <row r="294" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>3</v>
       </c>
@@ -13691,7 +13714,7 @@
       </c>
       <c r="AB294" s="4"/>
     </row>
-    <row r="295" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>3</v>
       </c>
@@ -13718,7 +13741,7 @@
       </c>
       <c r="AB295" s="4"/>
     </row>
-    <row r="296" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>3</v>
       </c>
@@ -13745,7 +13768,7 @@
       </c>
       <c r="AB296" s="4"/>
     </row>
-    <row r="297" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>3</v>
       </c>
@@ -13772,7 +13795,7 @@
       </c>
       <c r="AB297" s="4"/>
     </row>
-    <row r="298" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>3</v>
       </c>
@@ -13785,26 +13808,815 @@
       <c r="D298" s="3">
         <v>15</v>
       </c>
-      <c r="X298" s="8">
+      <c r="X298" s="1">
         <v>0.54400000000000004</v>
       </c>
-      <c r="Y298" s="8">
+      <c r="Y298" s="1">
         <v>1.329</v>
       </c>
-      <c r="Z298" s="8">
+      <c r="Z298" s="1">
         <v>1.111</v>
       </c>
-      <c r="AA298" s="8">
+      <c r="AA298" s="1">
         <v>1.1080000000000001</v>
       </c>
       <c r="AB298" s="4"/>
     </row>
-    <row r="299" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>3</v>
+      </c>
+      <c r="B299">
+        <v>2025</v>
+      </c>
+      <c r="C299" t="s">
+        <v>4</v>
+      </c>
+      <c r="D299">
+        <v>1</v>
+      </c>
       <c r="X299" s="4"/>
-      <c r="Y299" s="4"/>
-      <c r="Z299" s="4"/>
-      <c r="AA299" s="4"/>
-      <c r="AB299" s="4"/>
+      <c r="Y299" s="2">
+        <v>1095226.1611734589</v>
+      </c>
+      <c r="Z299" s="2">
+        <v>1190837.5218535385</v>
+      </c>
+      <c r="AA299" s="2">
+        <v>1280614.7425406505</v>
+      </c>
+      <c r="AB299" s="2">
+        <v>1369244.3515330954</v>
+      </c>
+    </row>
+    <row r="300" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>3</v>
+      </c>
+      <c r="B300">
+        <v>2025</v>
+      </c>
+      <c r="C300" t="s">
+        <v>7</v>
+      </c>
+      <c r="D300">
+        <v>2</v>
+      </c>
+      <c r="Y300" s="2">
+        <v>732340.579512286</v>
+      </c>
+      <c r="Z300" s="2">
+        <v>811142.94563081942</v>
+      </c>
+      <c r="AA300" s="2">
+        <v>862057.43330023659</v>
+      </c>
+      <c r="AB300" s="2">
+        <v>922544.81090963236</v>
+      </c>
+    </row>
+    <row r="301" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>3</v>
+      </c>
+      <c r="B301">
+        <v>2025</v>
+      </c>
+      <c r="C301" t="s">
+        <v>9</v>
+      </c>
+      <c r="D301">
+        <v>3</v>
+      </c>
+      <c r="Y301" s="2">
+        <v>316410.61528471991</v>
+      </c>
+      <c r="Z301" s="2">
+        <v>331311.37862628658</v>
+      </c>
+      <c r="AA301" s="2">
+        <v>366456.87013610348</v>
+      </c>
+      <c r="AB301" s="2">
+        <v>391112.22441466141</v>
+      </c>
+    </row>
+    <row r="302" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>3</v>
+      </c>
+      <c r="B302">
+        <v>2025</v>
+      </c>
+      <c r="C302" t="s">
+        <v>10</v>
+      </c>
+      <c r="D302">
+        <v>4</v>
+      </c>
+      <c r="Y302" s="2">
+        <v>24493.292334832346</v>
+      </c>
+      <c r="Z302" s="2">
+        <v>26005.952595441948</v>
+      </c>
+      <c r="AA302" s="2">
+        <v>27810.985473358214</v>
+      </c>
+      <c r="AB302" s="2">
+        <v>29772.758579207286</v>
+      </c>
+    </row>
+    <row r="303" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>3</v>
+      </c>
+      <c r="B303">
+        <v>2025</v>
+      </c>
+      <c r="C303" t="s">
+        <v>11</v>
+      </c>
+      <c r="D303">
+        <v>5</v>
+      </c>
+      <c r="Y303" s="2">
+        <v>21532.586701941917</v>
+      </c>
+      <c r="Z303" s="2">
+        <v>23031.422022607891</v>
+      </c>
+      <c r="AA303" s="2">
+        <v>24508.887184086274</v>
+      </c>
+      <c r="AB303" s="2">
+        <v>26110.047902069688</v>
+      </c>
+    </row>
+    <row r="304" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>3</v>
+      </c>
+      <c r="B304">
+        <v>2025</v>
+      </c>
+      <c r="C304" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D304" s="3">
+        <v>6</v>
+      </c>
+      <c r="Y304" s="2">
+        <v>625841.58821019775</v>
+      </c>
+      <c r="Z304" s="2">
+        <v>678482.74205108359</v>
+      </c>
+      <c r="AA304" s="2">
+        <v>736358.69783244166</v>
+      </c>
+      <c r="AB304" s="2">
+        <v>780548.83552790503</v>
+      </c>
+    </row>
+    <row r="305" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>3</v>
+      </c>
+      <c r="B305">
+        <v>2025</v>
+      </c>
+      <c r="C305" t="s">
+        <v>13</v>
+      </c>
+      <c r="D305" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y305" s="2">
+        <v>459881.76089897036</v>
+      </c>
+      <c r="Z305" s="2">
+        <v>499470.24511679175</v>
+      </c>
+      <c r="AA305" s="2">
+        <v>546163.91914320993</v>
+      </c>
+      <c r="AB305" s="2">
+        <v>578562.77199055813</v>
+      </c>
+    </row>
+    <row r="306" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>3</v>
+      </c>
+      <c r="B306">
+        <v>2025</v>
+      </c>
+      <c r="C306" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D306" s="3">
+        <v>8</v>
+      </c>
+      <c r="Y306" s="2">
+        <v>79241.54267161648</v>
+      </c>
+      <c r="Z306" s="2">
+        <v>87774.190548050014</v>
+      </c>
+      <c r="AA306" s="2">
+        <v>94183.701013535829</v>
+      </c>
+      <c r="AB306" s="2">
+        <v>100522.55149259006</v>
+      </c>
+    </row>
+    <row r="307" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>3</v>
+      </c>
+      <c r="B307">
+        <v>2025</v>
+      </c>
+      <c r="C307" t="s">
+        <v>22</v>
+      </c>
+      <c r="D307">
+        <v>9</v>
+      </c>
+      <c r="Y307" s="2">
+        <v>1846335</v>
+      </c>
+      <c r="Z307" s="2">
+        <v>2006132</v>
+      </c>
+      <c r="AA307" s="2">
+        <v>2163477</v>
+      </c>
+      <c r="AB307" s="2">
+        <v>2306199</v>
+      </c>
+    </row>
+    <row r="308" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>3</v>
+      </c>
+      <c r="B308">
+        <v>2025</v>
+      </c>
+      <c r="C308" t="s">
+        <v>15</v>
+      </c>
+      <c r="D308">
+        <v>10</v>
+      </c>
+      <c r="Y308" s="2">
+        <v>41104.454990131722</v>
+      </c>
+      <c r="Z308" s="2">
+        <v>37878.704284207226</v>
+      </c>
+      <c r="AA308" s="2">
+        <v>32601.819042399249</v>
+      </c>
+      <c r="AB308" s="2">
+        <v>32222.823437232302</v>
+      </c>
+    </row>
+    <row r="309" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>3</v>
+      </c>
+      <c r="B309">
+        <v>2025</v>
+      </c>
+      <c r="C309" t="s">
+        <v>16</v>
+      </c>
+      <c r="D309">
+        <v>11</v>
+      </c>
+      <c r="Y309" s="2">
+        <v>-89874.115016166063</v>
+      </c>
+      <c r="Z309" s="2">
+        <v>-73552.114713765943</v>
+      </c>
+      <c r="AA309" s="2">
+        <v>-77662.664945209777</v>
+      </c>
+      <c r="AB309" s="2">
+        <v>-91776.266417094157</v>
+      </c>
+    </row>
+    <row r="310" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>3</v>
+      </c>
+      <c r="B310">
+        <v>2025</v>
+      </c>
+      <c r="C310" t="s">
+        <v>18</v>
+      </c>
+      <c r="D310">
+        <v>12</v>
+      </c>
+      <c r="Y310" s="2">
+        <v>1797566</v>
+      </c>
+      <c r="Z310" s="2">
+        <v>1970458</v>
+      </c>
+      <c r="AA310" s="2">
+        <v>2118416</v>
+      </c>
+      <c r="AB310" s="2">
+        <v>2246645</v>
+      </c>
+    </row>
+    <row r="311" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>3</v>
+      </c>
+      <c r="B311">
+        <v>2025</v>
+      </c>
+      <c r="C311" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D311" s="3">
+        <v>13</v>
+      </c>
+      <c r="Y311" s="4">
+        <v>0.247</v>
+      </c>
+      <c r="Z311" s="4">
+        <v>0.251</v>
+      </c>
+      <c r="AA311" s="4">
+        <v>0.254</v>
+      </c>
+      <c r="AB311" s="4">
+        <v>0.254</v>
+      </c>
+    </row>
+    <row r="312" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>3</v>
+      </c>
+      <c r="B312">
+        <v>2025</v>
+      </c>
+      <c r="C312" t="s">
+        <v>19</v>
+      </c>
+      <c r="D312" s="3">
+        <v>14</v>
+      </c>
+      <c r="Y312" s="2">
+        <v>7478.8</v>
+      </c>
+      <c r="Z312" s="2">
+        <v>7999.4</v>
+      </c>
+      <c r="AA312" s="2">
+        <v>8512.6</v>
+      </c>
+      <c r="AB312" s="2">
+        <v>9068.7000000000007</v>
+      </c>
+    </row>
+    <row r="313" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>3</v>
+      </c>
+      <c r="B313">
+        <v>2025</v>
+      </c>
+      <c r="C313" t="s">
+        <v>20</v>
+      </c>
+      <c r="D313" s="3">
+        <v>15</v>
+      </c>
+      <c r="Y313" s="1">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="Z313" s="1">
+        <v>1.24</v>
+      </c>
+      <c r="AA313" s="1">
+        <v>1.22</v>
+      </c>
+      <c r="AB313" s="1">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="314" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>3</v>
+      </c>
+      <c r="B314">
+        <v>2026</v>
+      </c>
+      <c r="C314" t="s">
+        <v>4</v>
+      </c>
+      <c r="D314">
+        <v>1</v>
+      </c>
+      <c r="Y314" s="2"/>
+      <c r="Z314" s="2">
+        <v>1188334.0996665941</v>
+      </c>
+      <c r="AA314" s="2">
+        <v>1264312.8092662839</v>
+      </c>
+      <c r="AB314" s="2">
+        <v>1336568.7043387492</v>
+      </c>
+      <c r="AC314" s="2">
+        <v>1414787.925783826</v>
+      </c>
+    </row>
+    <row r="315" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>3</v>
+      </c>
+      <c r="B315">
+        <v>2026</v>
+      </c>
+      <c r="C315" t="s">
+        <v>7</v>
+      </c>
+      <c r="D315">
+        <v>2</v>
+      </c>
+      <c r="Y315" s="2"/>
+      <c r="Z315" s="2">
+        <v>786213.57665036304</v>
+      </c>
+      <c r="AA315" s="2">
+        <v>844820.36328915344</v>
+      </c>
+      <c r="AB315" s="2">
+        <v>895667.08318510035</v>
+      </c>
+      <c r="AC315" s="2">
+        <v>947472.01326358924</v>
+      </c>
+    </row>
+    <row r="316" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>3</v>
+      </c>
+      <c r="B316">
+        <v>2026</v>
+      </c>
+      <c r="C316" t="s">
+        <v>9</v>
+      </c>
+      <c r="D316">
+        <v>3</v>
+      </c>
+      <c r="Y316" s="2"/>
+      <c r="Z316" s="2">
+        <v>346576.21905324073</v>
+      </c>
+      <c r="AA316" s="2">
+        <v>364261.55473266536</v>
+      </c>
+      <c r="AB316" s="2">
+        <v>382845.53538796201</v>
+      </c>
+      <c r="AC316" s="2">
+        <v>405806.24119030504</v>
+      </c>
+    </row>
+    <row r="317" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>3</v>
+      </c>
+      <c r="B317">
+        <v>2026</v>
+      </c>
+      <c r="C317" t="s">
+        <v>10</v>
+      </c>
+      <c r="D317">
+        <v>4</v>
+      </c>
+      <c r="Y317" s="2"/>
+      <c r="Z317" s="2">
+        <v>25978.559330048312</v>
+      </c>
+      <c r="AA317" s="2">
+        <v>27657.285340454415</v>
+      </c>
+      <c r="AB317" s="2">
+        <v>29405.704659175732</v>
+      </c>
+      <c r="AC317" s="2">
+        <v>31182.90717335272</v>
+      </c>
+    </row>
+    <row r="318" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>3</v>
+      </c>
+      <c r="B318">
+        <v>2026</v>
+      </c>
+      <c r="C318" t="s">
+        <v>11</v>
+      </c>
+      <c r="D318">
+        <v>5</v>
+      </c>
+      <c r="Y318" s="2"/>
+      <c r="Z318" s="2">
+        <v>25952.348330110806</v>
+      </c>
+      <c r="AA318" s="2">
+        <v>27395.529290336242</v>
+      </c>
+      <c r="AB318" s="2">
+        <v>28824.330797879978</v>
+      </c>
+      <c r="AC318" s="2">
+        <v>30370.48326884503</v>
+      </c>
+    </row>
+    <row r="319" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>3</v>
+      </c>
+      <c r="B319">
+        <v>2026</v>
+      </c>
+      <c r="C319" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D319" s="3">
+        <v>6</v>
+      </c>
+      <c r="Y319" s="2"/>
+      <c r="Z319" s="2">
+        <v>683033.0547271159</v>
+      </c>
+      <c r="AA319" s="2">
+        <v>718632.8770966595</v>
+      </c>
+      <c r="AB319" s="2">
+        <v>759052.59757183818</v>
+      </c>
+      <c r="AC319" s="2">
+        <v>798718.39196301124</v>
+      </c>
+    </row>
+    <row r="320" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>3</v>
+      </c>
+      <c r="B320">
+        <v>2026</v>
+      </c>
+      <c r="C320" t="s">
+        <v>13</v>
+      </c>
+      <c r="D320" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y320" s="2"/>
+      <c r="Z320" s="2">
+        <v>497593.58364029392</v>
+      </c>
+      <c r="AA320" s="2">
+        <v>521363.28840565751</v>
+      </c>
+      <c r="AB320" s="2">
+        <v>551609.62949239393</v>
+      </c>
+      <c r="AC320" s="2">
+        <v>580519.99561484857</v>
+      </c>
+    </row>
+    <row r="321" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>3</v>
+      </c>
+      <c r="B321">
+        <v>2026</v>
+      </c>
+      <c r="C321" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D321" s="3">
+        <v>8</v>
+      </c>
+      <c r="Y321" s="2"/>
+      <c r="Z321" s="2">
+        <v>83649.356551742298</v>
+      </c>
+      <c r="AA321" s="2">
+        <v>88963.101882504809</v>
+      </c>
+      <c r="AB321" s="2">
+        <v>94777.09630661727</v>
+      </c>
+      <c r="AC321" s="2">
+        <v>101093.18723230353</v>
+      </c>
+    </row>
+    <row r="322" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>3</v>
+      </c>
+      <c r="B322">
+        <v>2026</v>
+      </c>
+      <c r="C322" t="s">
+        <v>22</v>
+      </c>
+      <c r="D322">
+        <v>9</v>
+      </c>
+      <c r="Y322" s="2"/>
+      <c r="Z322" s="2">
+        <v>2006947.4186056112</v>
+      </c>
+      <c r="AA322" s="2">
+        <v>2126961.602876239</v>
+      </c>
+      <c r="AB322" s="2">
+        <v>2248628.4336742605</v>
+      </c>
+      <c r="AC322" s="2">
+        <v>2376152.8954213387</v>
+      </c>
+    </row>
+    <row r="323" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>3</v>
+      </c>
+      <c r="B323">
+        <v>2026</v>
+      </c>
+      <c r="C323" t="s">
+        <v>15</v>
+      </c>
+      <c r="D323">
+        <v>10</v>
+      </c>
+      <c r="Y323" s="2"/>
+      <c r="Z323" s="2">
+        <v>44836.217480807471</v>
+      </c>
+      <c r="AA323" s="2">
+        <v>33449.192306199962</v>
+      </c>
+      <c r="AB323" s="2">
+        <v>29871.803266152641</v>
+      </c>
+      <c r="AC323" s="2">
+        <v>30681.608624245389</v>
+      </c>
+    </row>
+    <row r="324" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>3</v>
+      </c>
+      <c r="B324">
+        <v>2026</v>
+      </c>
+      <c r="C324" t="s">
+        <v>16</v>
+      </c>
+      <c r="D324">
+        <v>11</v>
+      </c>
+      <c r="Y324" s="2"/>
+      <c r="Z324" s="2">
+        <v>-73552.114708858819</v>
+      </c>
+      <c r="AA324" s="2">
+        <v>-78407.69484760538</v>
+      </c>
+      <c r="AB324" s="2">
+        <v>-87664.867257275895</v>
+      </c>
+      <c r="AC324" s="2">
+        <v>-86233.935595821429</v>
+      </c>
+    </row>
+    <row r="325" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>3</v>
+      </c>
+      <c r="B325">
+        <v>2026</v>
+      </c>
+      <c r="C325" t="s">
+        <v>18</v>
+      </c>
+      <c r="D325">
+        <v>12</v>
+      </c>
+      <c r="Y325" s="2"/>
+      <c r="Z325" s="2">
+        <v>1978231.52137756</v>
+      </c>
+      <c r="AA325" s="2">
+        <v>2082003.1003348336</v>
+      </c>
+      <c r="AB325" s="2">
+        <v>2190835.3696831372</v>
+      </c>
+      <c r="AC325" s="2">
+        <v>2320600.5684497626</v>
+      </c>
+    </row>
+    <row r="326" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>3</v>
+      </c>
+      <c r="B326">
+        <v>2026</v>
+      </c>
+      <c r="C326" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D326" s="3">
+        <v>13</v>
+      </c>
+      <c r="Y326" s="2"/>
+      <c r="Z326" s="4">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="AA326" s="4">
+        <v>0.26</v>
+      </c>
+      <c r="AB326" s="4">
+        <v>0.26100000000000001</v>
+      </c>
+      <c r="AC326" s="4">
+        <v>0.26200000000000001</v>
+      </c>
+    </row>
+    <row r="327" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>3</v>
+      </c>
+      <c r="B327">
+        <v>2026</v>
+      </c>
+      <c r="C327" t="s">
+        <v>19</v>
+      </c>
+      <c r="D327" s="3">
+        <v>14</v>
+      </c>
+      <c r="Y327" s="2"/>
+      <c r="Z327" s="2">
+        <v>7756.7</v>
+      </c>
+      <c r="AA327" s="2">
+        <v>8188.1</v>
+      </c>
+      <c r="AB327" s="2">
+        <v>8615.1</v>
+      </c>
+      <c r="AC327" s="2">
+        <v>9077.2999999999993</v>
+      </c>
+    </row>
+    <row r="328" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>3</v>
+      </c>
+      <c r="B328">
+        <v>2026</v>
+      </c>
+      <c r="C328" t="s">
+        <v>20</v>
+      </c>
+      <c r="D328" s="3">
+        <v>15</v>
+      </c>
+      <c r="Y328" s="2"/>
+      <c r="Z328" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="AA328" s="1">
+        <v>1.08</v>
+      </c>
+      <c r="AB328" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AC328" s="1">
+        <v>1.06</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X253">
